--- a/PROJECT_OHRM/test_data/TrackerData.xlsx
+++ b/PROJECT_OHRM/test_data/TrackerData.xlsx
@@ -30,10 +30,10 @@
     <t>Capacity</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
     <t>Rahul Mulge Patil</t>
+  </si>
+  <si>
+    <t>James  Butler</t>
   </si>
 </sst>
 </file>
@@ -397,15 +397,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
